--- a/wk3/DAB_Sorting_Filtering_Python_Solutions.xlsx
+++ b/wk3/DAB_Sorting_Filtering_Python_Solutions.xlsx
@@ -1,23 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jatin/Desktop/Learnings/Upright/Student_Repo/wk3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17301BE7-AAD7-4178-BC13-F272B0A911A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{890DF1CC-9414-4941-ADB3-CD593C6D716B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="-4580" windowWidth="29180" windowHeight="21000" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Practice_Data" sheetId="1" r:id="rId1"/>
     <sheet name="Instructions" sheetId="2" r:id="rId2"/>
     <sheet name="Python_Solutions" sheetId="3" r:id="rId3"/>
     <sheet name="Solutions" sheetId="4" r:id="rId4"/>
+    <sheet name="Short by descending" sheetId="5" r:id="rId5"/>
+    <sheet name="Stort region" sheetId="6" r:id="rId6"/>
+    <sheet name="Custom Ending" sheetId="7" r:id="rId7"/>
+    <sheet name="Avg sales" sheetId="9" r:id="rId8"/>
+    <sheet name="Top sales" sheetId="8" r:id="rId9"/>
+    <sheet name="North sales" sheetId="10" r:id="rId10"/>
+    <sheet name="Electronic sales" sheetId="11" r:id="rId11"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Avg sales'!$A$1:$F$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Custom Ending'!$A$1:$F$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Electronic sales'!$A$1:$F$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'North sales'!$A$1:$F$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Short by descending'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Stort region'!$A$1:$F$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Top sales'!$A$1:$F$13</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -56,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="72">
   <si>
     <t>Order ID</t>
   </si>
@@ -291,9 +307,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -306,6 +322,22 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -322,7 +354,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -345,11 +377,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -357,7 +402,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1127,18 +1184,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
     <col min="5" max="5" width="7" customWidth="1"/>
     <col min="6" max="6" width="21" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1158,7 +1215,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>1001</v>
       </c>
@@ -1178,7 +1235,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>1002</v>
       </c>
@@ -1198,7 +1255,7 @@
         <v>46144</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>1003</v>
       </c>
@@ -1218,7 +1275,7 @@
         <v>46127</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>1004</v>
       </c>
@@ -1238,7 +1295,7 @@
         <v>46146</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>1005</v>
       </c>
@@ -1258,7 +1315,7 @@
         <v>46147</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>1006</v>
       </c>
@@ -1278,7 +1335,7 @@
         <v>46101</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>1007</v>
       </c>
@@ -1298,7 +1355,7 @@
         <v>46149</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>1008</v>
       </c>
@@ -1318,7 +1375,7 @@
         <v>46150</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>1009</v>
       </c>
@@ -1338,7 +1395,7 @@
         <v>46151</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>1010</v>
       </c>
@@ -1358,7 +1415,7 @@
         <v>46032</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>1011</v>
       </c>
@@ -1378,7 +1435,7 @@
         <v>46152</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>1012</v>
       </c>
@@ -1400,20 +1457,597 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{540BF304-B6CE-7A43-8B5C-DBD12938AC89}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="6" max="6" width="20.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="6">
+        <v>1001</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="6">
+        <v>1200</v>
+      </c>
+      <c r="F2" s="7">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="6">
+        <v>1002</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="6">
+        <v>450</v>
+      </c>
+      <c r="F3" s="7">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="6">
+        <v>1003</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="6">
+        <v>800</v>
+      </c>
+      <c r="F4" s="7">
+        <v>46127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="6">
+        <v>1004</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="6">
+        <v>150</v>
+      </c>
+      <c r="F5" s="7">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="6">
+        <v>1005</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="6">
+        <v>600</v>
+      </c>
+      <c r="F6" s="7">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="6">
+        <v>1006</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="6">
+        <v>200</v>
+      </c>
+      <c r="F7" s="7">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="6">
+        <v>1007</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="6">
+        <v>950</v>
+      </c>
+      <c r="F8" s="7">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="6">
+        <v>1008</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="6">
+        <v>500</v>
+      </c>
+      <c r="F9" s="7">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="6">
+        <v>1009</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="6">
+        <v>300</v>
+      </c>
+      <c r="F10" s="7">
+        <v>46151</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="6">
+        <v>1010</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1100</v>
+      </c>
+      <c r="F11" s="7">
+        <v>46032</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="6">
+        <v>1011</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="6">
+        <v>50</v>
+      </c>
+      <c r="F12" s="7">
+        <v>46152</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="6">
+        <v>1012</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="6">
+        <v>2000</v>
+      </c>
+      <c r="F13" s="7">
+        <v>46016</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F13" xr:uid="{540BF304-B6CE-7A43-8B5C-DBD12938AC89}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="North"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="4">
+      <customFilters>
+        <customFilter operator="greaterThan" val="500"/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5F4353E-FEA7-8743-B4CA-EB1361629631}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="6" max="6" width="34.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="6">
+        <v>1001</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="6">
+        <v>1200</v>
+      </c>
+      <c r="F2" s="7">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="6">
+        <v>1002</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="6">
+        <v>450</v>
+      </c>
+      <c r="F3" s="7">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="6">
+        <v>1003</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="6">
+        <v>800</v>
+      </c>
+      <c r="F4" s="7">
+        <v>46127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="6">
+        <v>1004</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="6">
+        <v>150</v>
+      </c>
+      <c r="F5" s="7">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="6">
+        <v>1005</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="6">
+        <v>600</v>
+      </c>
+      <c r="F6" s="7">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="6">
+        <v>1006</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="6">
+        <v>200</v>
+      </c>
+      <c r="F7" s="7">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="6">
+        <v>1007</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="6">
+        <v>950</v>
+      </c>
+      <c r="F8" s="7">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="6">
+        <v>1008</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="6">
+        <v>500</v>
+      </c>
+      <c r="F9" s="7">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="6">
+        <v>1009</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="6">
+        <v>300</v>
+      </c>
+      <c r="F10" s="7">
+        <v>46151</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="6">
+        <v>1010</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1100</v>
+      </c>
+      <c r="F11" s="7">
+        <v>46032</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A12" s="6">
+        <v>1011</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="6">
+        <v>50</v>
+      </c>
+      <c r="F12" s="7">
+        <v>46152</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="6">
+        <v>1012</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="6">
+        <v>2000</v>
+      </c>
+      <c r="F13" s="7">
+        <v>46016</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F13" xr:uid="{B5F4353E-FEA7-8743-B4CA-EB1361629631}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Electronics"/>
+        <filter val="Office Supplies"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="4">
+      <filters>
+        <filter val="1100"/>
+        <filter val="1200"/>
+        <filter val="50"/>
+        <filter val="800"/>
+        <filter val="950"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
@@ -1424,7 +2058,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>23</v>
       </c>
@@ -1435,7 +2069,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>23</v>
       </c>
@@ -1446,7 +2080,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>28</v>
       </c>
@@ -1457,7 +2091,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>31</v>
       </c>
@@ -1468,7 +2102,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>31</v>
       </c>
@@ -1479,7 +2113,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>36</v>
       </c>
@@ -1490,7 +2124,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>36</v>
       </c>
@@ -1509,13 +2143,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="3" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
@@ -1526,7 +2160,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>42</v>
       </c>
@@ -1537,7 +2171,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>45</v>
       </c>
@@ -1548,7 +2182,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="80" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>48</v>
       </c>
@@ -1559,7 +2193,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>51</v>
       </c>
@@ -1570,7 +2204,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>54</v>
       </c>
@@ -1581,7 +2215,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>57</v>
       </c>
@@ -1592,7 +2226,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>60</v>
       </c>
@@ -1603,7 +2237,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>63</v>
       </c>
@@ -1614,7 +2248,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>66</v>
       </c>
@@ -1625,7 +2259,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>69</v>
       </c>
@@ -1644,9 +2278,1404 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12ADCD5C-F03B-4947-A895-584DC24CE14A}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA595B25-6347-EF43-8B89-E8B35171C690}">
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="6" max="6" width="17.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="6">
+        <v>1012</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="6">
+        <v>2000</v>
+      </c>
+      <c r="F2" s="7">
+        <v>46016</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="6">
+        <v>1001</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="6">
+        <v>1200</v>
+      </c>
+      <c r="F3" s="7">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="6">
+        <v>1010</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="6">
+        <v>1100</v>
+      </c>
+      <c r="F4" s="7">
+        <v>46032</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="6">
+        <v>1007</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="6">
+        <v>950</v>
+      </c>
+      <c r="F5" s="7">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="6">
+        <v>1003</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="6">
+        <v>800</v>
+      </c>
+      <c r="F6" s="7">
+        <v>46127</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="6">
+        <v>1005</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="6">
+        <v>600</v>
+      </c>
+      <c r="F7" s="7">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="6">
+        <v>1008</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="6">
+        <v>500</v>
+      </c>
+      <c r="F8" s="7">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="6">
+        <v>1002</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="6">
+        <v>450</v>
+      </c>
+      <c r="F9" s="7">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A10" s="6">
+        <v>1009</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="6">
+        <v>300</v>
+      </c>
+      <c r="F10" s="7">
+        <v>46151</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A11" s="6">
+        <v>1006</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="6">
+        <v>200</v>
+      </c>
+      <c r="F11" s="7">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A12" s="6">
+        <v>1004</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="6">
+        <v>150</v>
+      </c>
+      <c r="F12" s="7">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A13" s="6">
+        <v>1011</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="6">
+        <v>50</v>
+      </c>
+      <c r="F13" s="7">
+        <v>46152</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F1" xr:uid="{BA595B25-6347-EF43-8B89-E8B35171C690}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F13">
+      <sortCondition descending="1" ref="E1:E13"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB75BB5F-D77D-D64D-AF6F-4145155F6564}">
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="6" max="6" width="17.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="6">
+        <v>1003</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="6">
+        <v>800</v>
+      </c>
+      <c r="F2" s="7">
+        <v>46127</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A3" s="6">
+        <v>1006</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="6">
+        <v>200</v>
+      </c>
+      <c r="F3" s="7">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A4" s="6">
+        <v>1011</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="6">
+        <v>50</v>
+      </c>
+      <c r="F4" s="7">
+        <v>46152</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="6">
+        <v>1001</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="6">
+        <v>1200</v>
+      </c>
+      <c r="F5" s="7">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="6">
+        <v>1005</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="6">
+        <v>600</v>
+      </c>
+      <c r="F6" s="7">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A7" s="6">
+        <v>1009</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="6">
+        <v>300</v>
+      </c>
+      <c r="F7" s="7">
+        <v>46151</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="6">
+        <v>1012</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="6">
+        <v>2000</v>
+      </c>
+      <c r="F8" s="7">
+        <v>46016</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="6">
+        <v>1002</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="6">
+        <v>450</v>
+      </c>
+      <c r="F9" s="7">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="6">
+        <v>1007</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="6">
+        <v>950</v>
+      </c>
+      <c r="F10" s="7">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="6">
+        <v>1010</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1100</v>
+      </c>
+      <c r="F11" s="7">
+        <v>46032</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A12" s="6">
+        <v>1004</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="6">
+        <v>150</v>
+      </c>
+      <c r="F12" s="7">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="6">
+        <v>1008</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="6">
+        <v>500</v>
+      </c>
+      <c r="F13" s="7">
+        <v>46150</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F13" xr:uid="{BB75BB5F-D77D-D64D-AF6F-4145155F6564}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F13">
+      <sortCondition ref="C1:C13"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2581E3EB-69D0-E347-8FC6-FB7B9B0A74DD}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="6" max="6" width="17.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="6">
+        <v>1001</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="6">
+        <v>1200</v>
+      </c>
+      <c r="F2" s="7">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="6">
+        <v>1002</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="6">
+        <v>450</v>
+      </c>
+      <c r="F3" s="7">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="6">
+        <v>1003</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="6">
+        <v>800</v>
+      </c>
+      <c r="F4" s="7">
+        <v>46127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A5" s="6">
+        <v>1004</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="6">
+        <v>150</v>
+      </c>
+      <c r="F5" s="7">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="6">
+        <v>1005</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="6">
+        <v>600</v>
+      </c>
+      <c r="F6" s="7">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="6">
+        <v>1006</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="6">
+        <v>200</v>
+      </c>
+      <c r="F7" s="7">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="6">
+        <v>1007</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="6">
+        <v>950</v>
+      </c>
+      <c r="F8" s="7">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="6">
+        <v>1008</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="6">
+        <v>500</v>
+      </c>
+      <c r="F9" s="7">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A10" s="6">
+        <v>1009</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="6">
+        <v>300</v>
+      </c>
+      <c r="F10" s="7">
+        <v>46151</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="6">
+        <v>1010</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1100</v>
+      </c>
+      <c r="F11" s="7">
+        <v>46032</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="6">
+        <v>1011</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="6">
+        <v>50</v>
+      </c>
+      <c r="F12" s="7">
+        <v>46152</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="6">
+        <v>1012</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="6">
+        <v>2000</v>
+      </c>
+      <c r="F13" s="7">
+        <v>46016</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F13" xr:uid="{2581E3EB-69D0-E347-8FC6-FB7B9B0A74DD}">
+    <filterColumn colId="1">
+      <customFilters>
+        <customFilter val="*e"/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E0482A0-F4CD-A549-A944-D4323F7C1524}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="6" max="6" width="25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="6">
+        <v>1001</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="6">
+        <v>1200</v>
+      </c>
+      <c r="F2" s="7">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="6">
+        <v>1002</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="6">
+        <v>450</v>
+      </c>
+      <c r="F3" s="7">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="6">
+        <v>1003</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="6">
+        <v>800</v>
+      </c>
+      <c r="F4" s="7">
+        <v>46127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="6">
+        <v>1004</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="6">
+        <v>150</v>
+      </c>
+      <c r="F5" s="7">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="6">
+        <v>1005</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="6">
+        <v>600</v>
+      </c>
+      <c r="F6" s="7">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="6">
+        <v>1006</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="6">
+        <v>200</v>
+      </c>
+      <c r="F7" s="7">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="6">
+        <v>1007</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="6">
+        <v>950</v>
+      </c>
+      <c r="F8" s="7">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="6">
+        <v>1008</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="6">
+        <v>500</v>
+      </c>
+      <c r="F9" s="7">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="6">
+        <v>1009</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="6">
+        <v>300</v>
+      </c>
+      <c r="F10" s="7">
+        <v>46151</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="6">
+        <v>1010</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1100</v>
+      </c>
+      <c r="F11" s="7">
+        <v>46032</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="6">
+        <v>1011</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="6">
+        <v>50</v>
+      </c>
+      <c r="F12" s="7">
+        <v>46152</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="6">
+        <v>1012</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="6">
+        <v>2000</v>
+      </c>
+      <c r="F13" s="7">
+        <v>46016</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F13" xr:uid="{2E0482A0-F4CD-A549-A944-D4323F7C1524}">
+    <filterColumn colId="4">
+      <dynamicFilter type="aboveAverage" val="691.66666666666663"/>
+    </filterColumn>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{306C5A3B-1F16-0B46-9E85-9C3242820A66}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="6" max="6" width="17.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="6">
+        <v>1001</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="6">
+        <v>1200</v>
+      </c>
+      <c r="F2" s="7">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="6">
+        <v>1002</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="6">
+        <v>450</v>
+      </c>
+      <c r="F3" s="7">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="6">
+        <v>1003</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="6">
+        <v>800</v>
+      </c>
+      <c r="F4" s="7">
+        <v>46127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="6">
+        <v>1004</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="6">
+        <v>150</v>
+      </c>
+      <c r="F5" s="7">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="6">
+        <v>1005</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="6">
+        <v>600</v>
+      </c>
+      <c r="F6" s="7">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="6">
+        <v>1006</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="6">
+        <v>200</v>
+      </c>
+      <c r="F7" s="7">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="6">
+        <v>1007</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="6">
+        <v>950</v>
+      </c>
+      <c r="F8" s="7">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="16" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="6">
+        <v>1008</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="6">
+        <v>500</v>
+      </c>
+      <c r="F9" s="7">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="6">
+        <v>1009</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="6">
+        <v>300</v>
+      </c>
+      <c r="F10" s="7">
+        <v>46151</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="6">
+        <v>1010</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1100</v>
+      </c>
+      <c r="F11" s="7">
+        <v>46032</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="32" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="6">
+        <v>1011</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="6">
+        <v>50</v>
+      </c>
+      <c r="F12" s="7">
+        <v>46152</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="6">
+        <v>1012</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="6">
+        <v>2000</v>
+      </c>
+      <c r="F13" s="7">
+        <v>46016</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F13" xr:uid="{306C5A3B-1F16-0B46-9E85-9C3242820A66}">
+    <filterColumn colId="4">
+      <top10 val="3" filterVal="1100"/>
+    </filterColumn>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>